--- a/artfynd/A 57977-2025 artfynd.xlsx
+++ b/artfynd/A 57977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130361306</v>
       </c>
       <c r="B2" t="n">
-        <v>93002</v>
+        <v>93005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>130361277</v>
       </c>
       <c r="B3" t="n">
-        <v>96516</v>
+        <v>96519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57977-2025 artfynd.xlsx
+++ b/artfynd/A 57977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130361306</v>
       </c>
       <c r="B2" t="n">
-        <v>93005</v>
+        <v>93031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>130361277</v>
       </c>
       <c r="B3" t="n">
-        <v>96519</v>
+        <v>96545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57977-2025 artfynd.xlsx
+++ b/artfynd/A 57977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130361306</v>
       </c>
       <c r="B2" t="n">
-        <v>93031</v>
+        <v>93032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>130361277</v>
       </c>
       <c r="B3" t="n">
-        <v>96545</v>
+        <v>96546</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57977-2025 artfynd.xlsx
+++ b/artfynd/A 57977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130361306</v>
       </c>
       <c r="B2" t="n">
-        <v>93032</v>
+        <v>93033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>130361277</v>
       </c>
       <c r="B3" t="n">
-        <v>96546</v>
+        <v>96547</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57977-2025 artfynd.xlsx
+++ b/artfynd/A 57977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130361306</v>
       </c>
       <c r="B2" t="n">
-        <v>93033</v>
+        <v>93035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>130361277</v>
       </c>
       <c r="B3" t="n">
-        <v>96547</v>
+        <v>96549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57977-2025 artfynd.xlsx
+++ b/artfynd/A 57977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130361306</v>
       </c>
       <c r="B2" t="n">
-        <v>93035</v>
+        <v>93039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>130361277</v>
       </c>
       <c r="B3" t="n">
-        <v>96549</v>
+        <v>96553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57977-2025 artfynd.xlsx
+++ b/artfynd/A 57977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130361306</v>
       </c>
       <c r="B2" t="n">
-        <v>93039</v>
+        <v>93052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>130361277</v>
       </c>
       <c r="B3" t="n">
-        <v>96553</v>
+        <v>96566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57977-2025 artfynd.xlsx
+++ b/artfynd/A 57977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130361306</v>
       </c>
       <c r="B2" t="n">
-        <v>93052</v>
+        <v>93053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>130361277</v>
       </c>
       <c r="B3" t="n">
-        <v>96566</v>
+        <v>96567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57977-2025 artfynd.xlsx
+++ b/artfynd/A 57977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130361306</v>
       </c>
       <c r="B2" t="n">
-        <v>93053</v>
+        <v>93054</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>130361277</v>
       </c>
       <c r="B3" t="n">
-        <v>96567</v>
+        <v>96570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57977-2025 artfynd.xlsx
+++ b/artfynd/A 57977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130361306</v>
       </c>
       <c r="B2" t="n">
-        <v>93054</v>
+        <v>93063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>130361277</v>
       </c>
       <c r="B3" t="n">
-        <v>96570</v>
+        <v>96579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57977-2025 artfynd.xlsx
+++ b/artfynd/A 57977-2025 artfynd.xlsx
@@ -675,45 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130361306</v>
+        <v>130361277</v>
       </c>
       <c r="B2" t="n">
-        <v>93063</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583618</v>
+        <v>583640</v>
       </c>
       <c r="R2" t="n">
-        <v>6399180</v>
+        <v>6399064</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,14 +754,14 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Lite osäker, kan vara ngn liknande art - dock inte dropptaggsvamp</t>
+          <t>Många större kuddar</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -788,38 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130361277</v>
+        <v>130361306</v>
       </c>
       <c r="B3" t="n">
-        <v>96579</v>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583640</v>
+        <v>583618</v>
       </c>
       <c r="R3" t="n">
-        <v>6399064</v>
+        <v>6399180</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,14 +867,14 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Många större kuddar</t>
+          <t>Lite osäker, kan vara ngn liknande art - dock inte dropptaggsvamp</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
